--- a/grupos/2ALCV - Estadisticos 20232.xlsx
+++ b/grupos/2ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
@@ -227,43 +227,82 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>CUAPIO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>FRANCISCO XAVIER</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>SAMIR</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>FRANCISCO XAVIER</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
   </si>
 </sst>
 </file>
@@ -828,31 +867,31 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -882,7 +921,7 @@
         <v>-1</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>10</v>
@@ -894,10 +933,10 @@
         <v>5</v>
       </c>
       <c r="AG4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI4">
         <v>6</v>
@@ -906,7 +945,7 @@
         <v>-1</v>
       </c>
       <c r="AK4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -941,31 +980,31 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1007,10 +1046,10 @@
         <v>5</v>
       </c>
       <c r="AG5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5">
         <v>5</v>
@@ -1054,31 +1093,31 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1108,7 +1147,7 @@
         <v>-1</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD6">
         <v>7</v>
@@ -1123,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="AH6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI6">
         <v>5</v>
@@ -1132,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="AK6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1167,31 +1206,31 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1230,13 +1269,13 @@
         <v>9</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI7">
         <v>6</v>
@@ -1245,7 +1284,7 @@
         <v>-1</v>
       </c>
       <c r="AK7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1280,31 +1319,31 @@
         <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1334,19 +1373,19 @@
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD8">
         <v>9</v>
       </c>
       <c r="AE8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF8">
         <v>6</v>
       </c>
       <c r="AG8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8">
         <v>7</v>
@@ -1358,7 +1397,7 @@
         <v>-1</v>
       </c>
       <c r="AK8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1393,31 +1432,31 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1447,22 +1486,22 @@
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD9">
         <v>7</v>
       </c>
       <c r="AE9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI9">
         <v>6</v>
@@ -1506,31 +1545,31 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1560,31 +1599,31 @@
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE10">
         <v>7</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ10">
         <v>-1</v>
       </c>
       <c r="AK10">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1619,31 +1658,31 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1679,25 +1718,25 @@
         <v>8</v>
       </c>
       <c r="AE11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH11">
         <v>7</v>
       </c>
       <c r="AI11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ11">
         <v>-1</v>
       </c>
       <c r="AK11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1732,31 +1771,31 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1789,10 +1828,10 @@
         <v>5</v>
       </c>
       <c r="AD12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF12">
         <v>5</v>
@@ -1845,31 +1884,31 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1905,10 +1944,10 @@
         <v>7</v>
       </c>
       <c r="AE13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG13">
         <v>6</v>
@@ -1923,7 +1962,7 @@
         <v>-1</v>
       </c>
       <c r="AK13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -1958,31 +1997,31 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2015,7 +2054,7 @@
         <v>5</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE14">
         <v>5</v>
@@ -2024,10 +2063,10 @@
         <v>5</v>
       </c>
       <c r="AG14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI14">
         <v>5</v>
@@ -2071,31 +2110,31 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2128,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="AD15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE15">
         <v>7</v>
@@ -2137,10 +2176,10 @@
         <v>5</v>
       </c>
       <c r="AG15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI15">
         <v>5</v>
@@ -2149,7 +2188,7 @@
         <v>-1</v>
       </c>
       <c r="AK15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2184,31 +2223,31 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2253,7 +2292,7 @@
         <v>5</v>
       </c>
       <c r="AH16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI16">
         <v>5</v>
@@ -2262,7 +2301,7 @@
         <v>-1</v>
       </c>
       <c r="AK16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2297,31 +2336,31 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2363,10 +2402,10 @@
         <v>5</v>
       </c>
       <c r="AG17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI17">
         <v>5</v>
@@ -2410,31 +2449,31 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2464,7 +2503,7 @@
         <v>-1</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD18">
         <v>7</v>
@@ -2479,7 +2518,7 @@
         <v>5</v>
       </c>
       <c r="AH18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI18">
         <v>5</v>
@@ -2523,31 +2562,31 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2580,19 +2619,19 @@
         <v>6</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF19">
         <v>5</v>
       </c>
       <c r="AG19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI19">
         <v>5</v>
@@ -2601,7 +2640,7 @@
         <v>-1</v>
       </c>
       <c r="AK19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2636,31 +2675,31 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2690,10 +2729,10 @@
         <v>-1</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE20">
         <v>5</v>
@@ -2705,7 +2744,7 @@
         <v>5</v>
       </c>
       <c r="AH20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI20">
         <v>5</v>
@@ -2714,7 +2753,7 @@
         <v>-1</v>
       </c>
       <c r="AK20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2749,31 +2788,31 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2806,7 +2845,7 @@
         <v>5</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE21">
         <v>6</v>
@@ -2862,31 +2901,31 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2922,16 +2961,16 @@
         <v>7</v>
       </c>
       <c r="AE22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF22">
         <v>5</v>
       </c>
       <c r="AG22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI22">
         <v>6</v>
@@ -2975,31 +3014,31 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3029,7 +3068,7 @@
         <v>-1</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD23">
         <v>8</v>
@@ -3038,22 +3077,22 @@
         <v>8</v>
       </c>
       <c r="AF23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG23">
+        <v>7</v>
+      </c>
+      <c r="AH23">
+        <v>8</v>
+      </c>
+      <c r="AI23">
+        <v>6</v>
+      </c>
+      <c r="AJ23">
+        <v>-1</v>
+      </c>
+      <c r="AK23">
         <v>9</v>
-      </c>
-      <c r="AH23">
-        <v>8</v>
-      </c>
-      <c r="AI23">
-        <v>6</v>
-      </c>
-      <c r="AJ23">
-        <v>-1</v>
-      </c>
-      <c r="AK23">
-        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3088,31 +3127,31 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3142,22 +3181,22 @@
         <v>-1</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF24">
         <v>5</v>
       </c>
       <c r="AG24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI24">
         <v>5</v>
@@ -3166,7 +3205,7 @@
         <v>-1</v>
       </c>
       <c r="AK24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3201,31 +3240,31 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3255,22 +3294,22 @@
         <v>-1</v>
       </c>
       <c r="AC25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD25">
         <v>8</v>
       </c>
       <c r="AE25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF25">
         <v>5</v>
       </c>
       <c r="AG25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI25">
         <v>5</v>
@@ -3314,31 +3353,31 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3371,19 +3410,19 @@
         <v>8</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26">
         <v>6</v>
@@ -3427,31 +3466,31 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3481,22 +3520,22 @@
         <v>-1</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE27">
         <v>6</v>
       </c>
       <c r="AF27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI27">
         <v>6</v>
@@ -3505,7 +3544,7 @@
         <v>-1</v>
       </c>
       <c r="AK27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3540,31 +3579,31 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3600,13 +3639,13 @@
         <v>6</v>
       </c>
       <c r="AE28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF28">
         <v>5</v>
       </c>
       <c r="AG28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH28">
         <v>7</v>
@@ -3653,31 +3692,31 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3719,10 +3758,10 @@
         <v>5</v>
       </c>
       <c r="AG29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI29">
         <v>5</v>
@@ -3766,31 +3805,31 @@
         <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3820,22 +3859,22 @@
         <v>-1</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF30">
         <v>5</v>
       </c>
       <c r="AG30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI30">
         <v>6</v>
@@ -3844,7 +3883,7 @@
         <v>-1</v>
       </c>
       <c r="AK30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -3879,31 +3918,31 @@
         <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -3936,19 +3975,19 @@
         <v>5</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF31">
         <v>5</v>
       </c>
       <c r="AG31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI31">
         <v>5</v>
@@ -3992,31 +4031,31 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -4046,31 +4085,31 @@
         <v>-1</v>
       </c>
       <c r="AC32">
+        <v>8</v>
+      </c>
+      <c r="AD32">
+        <v>8</v>
+      </c>
+      <c r="AE32">
+        <v>8</v>
+      </c>
+      <c r="AF32">
+        <v>5</v>
+      </c>
+      <c r="AG32">
+        <v>5</v>
+      </c>
+      <c r="AH32">
         <v>9</v>
       </c>
-      <c r="AD32">
-        <v>8</v>
-      </c>
-      <c r="AE32">
+      <c r="AI32">
+        <v>5</v>
+      </c>
+      <c r="AJ32">
+        <v>-1</v>
+      </c>
+      <c r="AK32">
         <v>9</v>
-      </c>
-      <c r="AF32">
-        <v>5</v>
-      </c>
-      <c r="AG32">
-        <v>6</v>
-      </c>
-      <c r="AH32">
-        <v>8</v>
-      </c>
-      <c r="AI32">
-        <v>5</v>
-      </c>
-      <c r="AJ32">
-        <v>-1</v>
-      </c>
-      <c r="AK32">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4251,25 +4290,25 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O4">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4278,25 +4317,25 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X4">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Y4">
         <v>100</v>
       </c>
       <c r="Z4">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -4337,10 +4376,10 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>83.3</v>
+        <v>72.7</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -4349,25 +4388,25 @@
         <v>93.8</v>
       </c>
       <c r="O5">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="S5">
         <v>100</v>
       </c>
       <c r="T5">
-        <v>83.3</v>
+        <v>72.7</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4376,16 +4415,16 @@
         <v>93.8</v>
       </c>
       <c r="X5">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Y5">
         <v>100</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="AB5">
         <v>100</v>
@@ -4423,58 +4462,58 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>91.7</v>
+        <v>81.8</v>
       </c>
       <c r="L6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O6">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>90</v>
+        <v>66.7</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T6">
-        <v>91.7</v>
+        <v>81.8</v>
       </c>
       <c r="U6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V6">
         <v>100</v>
       </c>
       <c r="W6">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X6">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Y6">
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>90</v>
+        <v>66.7</v>
       </c>
       <c r="AA6">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="AB6">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -4509,10 +4548,10 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -4536,10 +4575,10 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4595,10 +4634,10 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4622,10 +4661,10 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4681,7 +4720,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -4699,7 +4738,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4708,7 +4747,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -4726,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="Z9">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AA9">
         <v>100</v>
@@ -4767,25 +4806,25 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L10">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="O10">
         <v>93.8</v>
       </c>
-      <c r="O10">
-        <v>87.5</v>
-      </c>
       <c r="P10">
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>80</v>
+        <v>90.5</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4794,25 +4833,25 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U10">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="X10">
         <v>93.8</v>
       </c>
-      <c r="X10">
-        <v>87.5</v>
-      </c>
       <c r="Y10">
         <v>100</v>
       </c>
       <c r="Z10">
-        <v>80</v>
+        <v>90.5</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -4853,52 +4892,52 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L11">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O11">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="P11">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>95.2</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="U11">
         <v>87.5</v>
       </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-      <c r="Q11">
-        <v>90</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
-        <v>83.3</v>
-      </c>
-      <c r="U11">
-        <v>90</v>
-      </c>
       <c r="V11">
         <v>100</v>
       </c>
       <c r="W11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X11">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y11">
         <v>100</v>
       </c>
       <c r="Z11">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -4939,25 +4978,25 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O12">
-        <v>93.8</v>
+        <v>81.3</v>
       </c>
       <c r="P12">
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4966,25 +5005,25 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V12">
         <v>100</v>
       </c>
       <c r="W12">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X12">
-        <v>93.8</v>
+        <v>81.3</v>
       </c>
       <c r="Y12">
         <v>100</v>
       </c>
       <c r="Z12">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -5025,25 +5064,25 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>91.7</v>
+        <v>77.3</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O13">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>80</v>
+        <v>73.8</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -5052,25 +5091,25 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>91.7</v>
+        <v>77.3</v>
       </c>
       <c r="U13">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X13">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Y13">
         <v>100</v>
       </c>
       <c r="Z13">
-        <v>80</v>
+        <v>73.8</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -5111,58 +5150,58 @@
         <v>90</v>
       </c>
       <c r="K14">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="L14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O14">
-        <v>68.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="T14">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="U14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="X14">
-        <v>68.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Y14">
         <v>100</v>
       </c>
       <c r="Z14">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="AA14">
         <v>100</v>
       </c>
       <c r="AB14">
-        <v>90</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -5197,16 +5236,16 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O15">
         <v>81.3</v>
@@ -5215,7 +5254,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -5224,16 +5263,16 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="U15">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X15">
         <v>81.3</v>
@@ -5242,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="Z15">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -5283,10 +5322,10 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="L16">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -5295,25 +5334,25 @@
         <v>93.8</v>
       </c>
       <c r="O16">
-        <v>87.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>61.8</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="U16">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -5322,16 +5361,16 @@
         <v>93.8</v>
       </c>
       <c r="X16">
-        <v>87.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Y16">
         <v>100</v>
       </c>
       <c r="Z16">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="AA16">
-        <v>100</v>
+        <v>61.8</v>
       </c>
       <c r="AB16">
         <v>100</v>
@@ -5369,7 +5408,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5381,22 +5420,22 @@
         <v>93.8</v>
       </c>
       <c r="O17">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T17">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -5408,19 +5447,19 @@
         <v>93.8</v>
       </c>
       <c r="X17">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y17">
         <v>100</v>
       </c>
       <c r="Z17">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="AA17">
         <v>100</v>
       </c>
       <c r="AB17">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -5455,10 +5494,10 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L18">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -5467,25 +5506,25 @@
         <v>93.8</v>
       </c>
       <c r="O18">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T18">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U18">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5494,19 +5533,19 @@
         <v>93.8</v>
       </c>
       <c r="X18">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Y18">
         <v>100</v>
       </c>
       <c r="Z18">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="AA18">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="AB18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -5541,16 +5580,16 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -5559,7 +5598,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5568,16 +5607,16 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V19">
         <v>100</v>
       </c>
       <c r="W19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -5586,7 +5625,7 @@
         <v>100</v>
       </c>
       <c r="Z19">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="AA19">
         <v>100</v>
@@ -5627,55 +5666,55 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L20">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U20">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="Y20">
         <v>100</v>
       </c>
       <c r="Z20">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="AA20">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="AB20">
         <v>100</v>
@@ -5713,16 +5752,16 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L21">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="O21">
         <v>87.5</v>
@@ -5731,7 +5770,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5740,16 +5779,16 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U21">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="X21">
         <v>87.5</v>
@@ -5758,7 +5797,7 @@
         <v>100</v>
       </c>
       <c r="Z21">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="AA21">
         <v>100</v>
@@ -5799,7 +5838,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5808,7 +5847,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -5817,7 +5856,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5826,7 +5865,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5835,7 +5874,7 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -5844,7 +5883,7 @@
         <v>100</v>
       </c>
       <c r="Z22">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="AA22">
         <v>100</v>
@@ -5885,7 +5924,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5894,25 +5933,25 @@
         <v>100</v>
       </c>
       <c r="N23">
+        <v>87.5</v>
+      </c>
+      <c r="O23">
         <v>93.8</v>
       </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="S23">
         <v>100</v>
       </c>
       <c r="T23">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5921,19 +5960,19 @@
         <v>100</v>
       </c>
       <c r="W23">
+        <v>87.5</v>
+      </c>
+      <c r="X23">
         <v>93.8</v>
       </c>
-      <c r="X23">
-        <v>100</v>
-      </c>
       <c r="Y23">
         <v>100</v>
       </c>
       <c r="Z23">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="AA23">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="AB23">
         <v>100</v>
@@ -5971,55 +6010,55 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
+        <v>87.5</v>
+      </c>
+      <c r="O24">
         <v>93.8</v>
       </c>
-      <c r="O24">
+      <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>95.2</v>
+      </c>
+      <c r="R24">
+        <v>91.2</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
+        <v>95.5</v>
+      </c>
+      <c r="U24">
+        <v>90</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+      <c r="W24">
         <v>87.5</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>90</v>
-      </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
-      <c r="S24">
-        <v>100</v>
-      </c>
-      <c r="T24">
-        <v>91.7</v>
-      </c>
-      <c r="U24">
-        <v>100</v>
-      </c>
-      <c r="V24">
-        <v>100</v>
-      </c>
-      <c r="W24">
+      <c r="X24">
         <v>93.8</v>
       </c>
-      <c r="X24">
-        <v>87.5</v>
-      </c>
       <c r="Y24">
         <v>100</v>
       </c>
       <c r="Z24">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="AA24">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="AB24">
         <v>100</v>
@@ -6057,25 +6096,25 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O25">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P25">
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -6084,25 +6123,25 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V25">
         <v>100</v>
       </c>
       <c r="W25">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X25">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y25">
         <v>100</v>
       </c>
       <c r="Z25">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="AA25">
         <v>100</v>
@@ -6143,10 +6182,10 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -6161,7 +6200,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -6170,10 +6209,10 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -6188,7 +6227,7 @@
         <v>100</v>
       </c>
       <c r="Z26">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="AA26">
         <v>100</v>
@@ -6229,7 +6268,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -6238,16 +6277,16 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O27">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P27">
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>80</v>
+        <v>73.8</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -6256,7 +6295,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6265,16 +6304,16 @@
         <v>100</v>
       </c>
       <c r="W27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X27">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y27">
         <v>100</v>
       </c>
       <c r="Z27">
-        <v>80</v>
+        <v>73.8</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -6315,10 +6354,10 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -6333,7 +6372,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -6342,10 +6381,10 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -6360,7 +6399,7 @@
         <v>100</v>
       </c>
       <c r="Z28">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="AA28">
         <v>100</v>
@@ -6401,10 +6440,10 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L29">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -6419,19 +6458,19 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T29">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U29">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6446,13 +6485,13 @@
         <v>100</v>
       </c>
       <c r="Z29">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="AA29">
         <v>100</v>
       </c>
       <c r="AB29">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="30" spans="1:28">
@@ -6487,7 +6526,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L30">
         <v>95</v>
@@ -6499,7 +6538,7 @@
         <v>93.8</v>
       </c>
       <c r="O30">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6514,7 +6553,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U30">
         <v>95</v>
@@ -6526,7 +6565,7 @@
         <v>93.8</v>
       </c>
       <c r="X30">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y30">
         <v>100</v>
@@ -6573,7 +6612,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -6591,7 +6630,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -6600,7 +6639,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -6618,7 +6657,7 @@
         <v>100</v>
       </c>
       <c r="Z31">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="AA31">
         <v>100</v>
@@ -6671,13 +6710,13 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -6698,13 +6737,13 @@
         <v>100</v>
       </c>
       <c r="X32">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y32">
         <v>100</v>
       </c>
       <c r="Z32">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="AA32">
         <v>100</v>
@@ -6805,16 +6844,16 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>24.1</v>
+        <v>20.7</v>
       </c>
       <c r="G3" s="2">
-        <v>75.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H3">
         <v>5.3</v>
@@ -6837,19 +6876,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2">
-        <v>37.9</v>
+        <v>44.8</v>
       </c>
       <c r="G4" s="2">
-        <v>62.1</v>
+        <v>55.2</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6860,7 +6899,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -6892,7 +6931,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -6901,19 +6940,19 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>48.3</v>
+        <v>62.1</v>
       </c>
       <c r="G6" s="2">
-        <v>51.7</v>
+        <v>37.9</v>
       </c>
       <c r="H6">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6933,19 +6972,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
-        <v>48.3</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2">
-        <v>51.7</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6965,19 +7004,19 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>55.2</v>
+        <v>79.3</v>
       </c>
       <c r="G8" s="2">
-        <v>44.8</v>
+        <v>20.7</v>
       </c>
       <c r="H8">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7029,19 +7068,19 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2">
-        <v>100</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G10" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="H10">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7091,7 +7130,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7123,22 +7162,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920222</v>
+        <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7146,16 +7185,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920222</v>
+        <v>23330051920218</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -7169,22 +7208,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920318</v>
+        <v>23330051920230</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7192,16 +7231,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920318</v>
+        <v>23330051920230</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -7215,39 +7254,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920221</v>
+        <v>23330051920247</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920223</v>
+        <v>23330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -7261,24 +7300,185 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920247</v>
+        <v>23330051920258</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920258</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920265</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920265</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920221</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920223</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920404</v>
+      </c>
+      <c r="B14" t="s">
         <v>76</v>
       </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F14" t="s">
         <v>56</v>
       </c>
-      <c r="G8">
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920318</v>
+      </c>
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20232.xlsx
+++ b/grupos/2ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -191,30 +191,30 @@
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,31 +227,52 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
     <t>ALMANZA</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>SANTOS</t>
@@ -260,49 +281,94 @@
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>MIREILLE</t>
   </si>
   <si>
     <t>VANESA BETHSABE</t>
   </si>
   <si>
-    <t>JAIRO</t>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>FRANCISCO XAVIER</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
   </si>
   <si>
     <t>RAYMUNDO</t>
   </si>
   <si>
+    <t>SAMIR</t>
+  </si>
+  <si>
     <t>AIDE SCARLET</t>
   </si>
   <si>
     <t>KAREN</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>FRANCISCO XAVIER</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
   </si>
 </sst>
 </file>
@@ -894,31 +960,31 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>-1</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -930,10 +996,10 @@
         <v>7</v>
       </c>
       <c r="AF4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH4">
         <v>8</v>
@@ -1007,31 +1073,31 @@
         <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>-1</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1040,13 +1106,13 @@
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH5">
         <v>6</v>
@@ -1120,43 +1186,43 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>-1</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>5</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE6">
         <v>6</v>
       </c>
       <c r="AF6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG6">
         <v>5</v>
@@ -1171,7 +1237,7 @@
         <v>-1</v>
       </c>
       <c r="AK6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1233,31 +1299,31 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>-1</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>6</v>
@@ -1269,10 +1335,10 @@
         <v>9</v>
       </c>
       <c r="AF7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7">
         <v>7</v>
@@ -1284,7 +1350,7 @@
         <v>-1</v>
       </c>
       <c r="AK7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1346,31 +1412,31 @@
         <v>7</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>-1</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1382,7 +1448,7 @@
         <v>7</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG8">
         <v>8</v>
@@ -1459,34 +1525,34 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>-1</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD9">
         <v>7</v>
@@ -1495,7 +1561,7 @@
         <v>7</v>
       </c>
       <c r="AF9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG9">
         <v>6</v>
@@ -1510,7 +1576,7 @@
         <v>-1</v>
       </c>
       <c r="AK9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1572,37 +1638,37 @@
         <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>-1</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE10">
         <v>7</v>
@@ -1611,7 +1677,7 @@
         <v>7</v>
       </c>
       <c r="AG10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH10">
         <v>6</v>
@@ -1685,46 +1751,46 @@
         <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>-1</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11">
         <v>7</v>
       </c>
       <c r="AF11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH11">
         <v>7</v>
@@ -1736,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="AK11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1798,46 +1864,46 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>-1</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>5</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE12">
         <v>7</v>
       </c>
       <c r="AF12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH12">
         <v>7</v>
@@ -1911,43 +1977,43 @@
         <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>-1</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>5</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>7</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>6</v>
@@ -2024,46 +2090,46 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>-1</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH14">
         <v>6</v>
@@ -2137,46 +2203,46 @@
         <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>-1</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>5</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15">
         <v>7</v>
       </c>
       <c r="AF15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH15">
         <v>6</v>
@@ -2250,46 +2316,46 @@
         <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>-1</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>5</v>
       </c>
       <c r="AD16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16">
         <v>6</v>
@@ -2363,46 +2429,46 @@
         <v>5</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>-1</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>5</v>
       </c>
       <c r="AD17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH17">
         <v>6</v>
@@ -2476,43 +2542,43 @@
         <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>-1</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE18">
         <v>6</v>
       </c>
       <c r="AF18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG18">
         <v>5</v>
@@ -2527,7 +2593,7 @@
         <v>-1</v>
       </c>
       <c r="AK18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2589,31 +2655,31 @@
         <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>-1</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2625,10 +2691,10 @@
         <v>7</v>
       </c>
       <c r="AF19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH19">
         <v>8</v>
@@ -2702,46 +2768,46 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>-1</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH20">
         <v>6</v>
@@ -2753,7 +2819,7 @@
         <v>-1</v>
       </c>
       <c r="AK20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2815,58 +2881,58 @@
         <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>-1</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE21">
         <v>6</v>
       </c>
       <c r="AF21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH21">
         <v>7</v>
       </c>
       <c r="AI21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ21">
         <v>-1</v>
       </c>
       <c r="AK21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -2928,34 +2994,34 @@
         <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>-1</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD22">
         <v>7</v>
@@ -2964,7 +3030,7 @@
         <v>7</v>
       </c>
       <c r="AF22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG22">
         <v>6</v>
@@ -3041,34 +3107,34 @@
         <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>-1</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD23">
         <v>8</v>
@@ -3080,7 +3146,7 @@
         <v>7</v>
       </c>
       <c r="AG23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH23">
         <v>8</v>
@@ -3154,46 +3220,46 @@
         <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>-1</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>6</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH24">
         <v>6</v>
@@ -3205,7 +3271,7 @@
         <v>-1</v>
       </c>
       <c r="AK24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3255,7 +3321,7 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -3267,31 +3333,31 @@
         <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>-1</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -3303,13 +3369,13 @@
         <v>7</v>
       </c>
       <c r="AF25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI25">
         <v>5</v>
@@ -3380,31 +3446,31 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>-1</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -3419,7 +3485,7 @@
         <v>7</v>
       </c>
       <c r="AG26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26">
         <v>9</v>
@@ -3493,31 +3559,31 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>-1</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>7</v>
@@ -3526,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="AE27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG27">
         <v>6</v>
@@ -3606,46 +3672,46 @@
         <v>6</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>-1</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>5</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE28">
         <v>7</v>
       </c>
       <c r="AF28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28">
         <v>7</v>
@@ -3657,7 +3723,7 @@
         <v>-1</v>
       </c>
       <c r="AK28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3719,43 +3785,43 @@
         <v>5</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>-1</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC29">
         <v>5</v>
       </c>
       <c r="AD29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG29">
         <v>7</v>
@@ -3832,31 +3898,31 @@
         <v>7</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>-1</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>-1</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3868,10 +3934,10 @@
         <v>7</v>
       </c>
       <c r="AF30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH30">
         <v>9</v>
@@ -3933,7 +3999,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>6</v>
@@ -3945,49 +4011,49 @@
         <v>6</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>-1</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>5</v>
       </c>
       <c r="AD31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI31">
         <v>5</v>
@@ -3996,7 +4062,7 @@
         <v>-1</v>
       </c>
       <c r="AK31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4058,31 +4124,31 @@
         <v>9</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>-1</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -4094,10 +4160,10 @@
         <v>8</v>
       </c>
       <c r="AF32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH32">
         <v>9</v>
@@ -4317,25 +4383,25 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U4">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X4">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y4">
         <v>100</v>
       </c>
       <c r="Z4">
-        <v>76.2</v>
+        <v>85.2</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -4403,25 +4469,25 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="U5">
+        <v>90</v>
+      </c>
+      <c r="V5">
+        <v>100</v>
+      </c>
+      <c r="W5">
+        <v>95.8</v>
+      </c>
+      <c r="X5">
         <v>87.5</v>
       </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-      <c r="W5">
-        <v>93.8</v>
-      </c>
-      <c r="X5">
-        <v>84.40000000000001</v>
-      </c>
       <c r="Y5">
         <v>100</v>
       </c>
       <c r="Z5">
-        <v>66.7</v>
+        <v>78.7</v>
       </c>
       <c r="AA5">
         <v>91.2</v>
@@ -4489,31 +4555,31 @@
         <v>93.3</v>
       </c>
       <c r="T6">
-        <v>81.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V6">
         <v>100</v>
       </c>
       <c r="W6">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="X6">
-        <v>87.5</v>
+        <v>83.3</v>
       </c>
       <c r="Y6">
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>66.7</v>
+        <v>78.7</v>
       </c>
       <c r="AA6">
         <v>91.2</v>
       </c>
       <c r="AB6">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -4575,10 +4641,10 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U7">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4661,19 +4727,19 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U8">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V8">
         <v>100</v>
       </c>
       <c r="W8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -4747,7 +4813,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -4756,7 +4822,7 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -4765,7 +4831,7 @@
         <v>100</v>
       </c>
       <c r="Z9">
-        <v>92.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AA9">
         <v>100</v>
@@ -4833,25 +4899,25 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>95.5</v>
+        <v>87.5</v>
       </c>
       <c r="U10">
-        <v>82.5</v>
+        <v>86.7</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="X10">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y10">
         <v>100</v>
       </c>
       <c r="Z10">
-        <v>90.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -4919,25 +4985,25 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U11">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="V11">
         <v>100</v>
       </c>
       <c r="W11">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="X11">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y11">
         <v>100</v>
       </c>
       <c r="Z11">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -5005,25 +5071,25 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>68.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U12">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V12">
         <v>100</v>
       </c>
       <c r="W12">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="X12">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="Y12">
         <v>100</v>
       </c>
       <c r="Z12">
-        <v>85.7</v>
+        <v>91.8</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -5091,25 +5157,25 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U13">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="X13">
-        <v>84.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y13">
         <v>100</v>
       </c>
       <c r="Z13">
-        <v>73.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -5177,31 +5243,31 @@
         <v>88.3</v>
       </c>
       <c r="T14">
-        <v>72.7</v>
+        <v>81.3</v>
       </c>
       <c r="U14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>78.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="X14">
-        <v>71.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Y14">
         <v>100</v>
       </c>
       <c r="Z14">
-        <v>76.2</v>
+        <v>85.2</v>
       </c>
       <c r="AA14">
         <v>100</v>
       </c>
       <c r="AB14">
-        <v>88.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -5263,16 +5329,16 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>81.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U15">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="X15">
         <v>81.3</v>
@@ -5281,7 +5347,7 @@
         <v>100</v>
       </c>
       <c r="Z15">
-        <v>81</v>
+        <v>88.5</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -5349,10 +5415,10 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>68.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="U16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -5361,13 +5427,13 @@
         <v>93.8</v>
       </c>
       <c r="X16">
-        <v>71.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Y16">
         <v>100</v>
       </c>
       <c r="Z16">
-        <v>66.7</v>
+        <v>78.7</v>
       </c>
       <c r="AA16">
         <v>61.8</v>
@@ -5435,7 +5501,7 @@
         <v>93.3</v>
       </c>
       <c r="T17">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -5447,19 +5513,19 @@
         <v>93.8</v>
       </c>
       <c r="X17">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Y17">
         <v>100</v>
       </c>
       <c r="Z17">
-        <v>76.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AA17">
         <v>100</v>
       </c>
       <c r="AB17">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -5521,10 +5587,10 @@
         <v>93.3</v>
       </c>
       <c r="T18">
-        <v>86.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="U18">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5533,19 +5599,19 @@
         <v>93.8</v>
       </c>
       <c r="X18">
-        <v>84.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="Y18">
         <v>100</v>
       </c>
       <c r="Z18">
-        <v>85.7</v>
+        <v>91.8</v>
       </c>
       <c r="AA18">
         <v>91.2</v>
       </c>
       <c r="AB18">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -5607,25 +5673,25 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U19">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V19">
         <v>100</v>
       </c>
       <c r="W19">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="X19">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Y19">
         <v>100</v>
       </c>
       <c r="Z19">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA19">
         <v>100</v>
@@ -5693,25 +5759,25 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U20">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="X20">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="Y20">
         <v>100</v>
       </c>
       <c r="Z20">
-        <v>76.2</v>
+        <v>85.2</v>
       </c>
       <c r="AA20">
         <v>91.2</v>
@@ -5779,10 +5845,10 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U21">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -5791,13 +5857,13 @@
         <v>87.5</v>
       </c>
       <c r="X21">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y21">
         <v>100</v>
       </c>
       <c r="Z21">
-        <v>81</v>
+        <v>73.8</v>
       </c>
       <c r="AA21">
         <v>100</v>
@@ -5865,7 +5931,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5874,7 +5940,7 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -5883,7 +5949,7 @@
         <v>100</v>
       </c>
       <c r="Z22">
-        <v>90.5</v>
+        <v>90.2</v>
       </c>
       <c r="AA22">
         <v>100</v>
@@ -5951,7 +6017,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5960,16 +6026,16 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X23">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y23">
         <v>100</v>
       </c>
       <c r="Z23">
-        <v>95.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AA23">
         <v>91.2</v>
@@ -6037,25 +6103,25 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>95.5</v>
+        <v>87.5</v>
       </c>
       <c r="U24">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X24">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y24">
         <v>100</v>
       </c>
       <c r="Z24">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AA24">
         <v>91.2</v>
@@ -6123,25 +6189,25 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U25">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="V25">
         <v>100</v>
       </c>
       <c r="W25">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="X25">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Y25">
         <v>100</v>
       </c>
       <c r="Z25">
-        <v>76.2</v>
+        <v>85.2</v>
       </c>
       <c r="AA25">
         <v>100</v>
@@ -6209,16 +6275,16 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U26">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="V26">
         <v>100</v>
       </c>
       <c r="W26">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -6227,7 +6293,7 @@
         <v>100</v>
       </c>
       <c r="Z26">
-        <v>95.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AA26">
         <v>100</v>
@@ -6295,25 +6361,25 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="X27">
-        <v>90.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="Y27">
         <v>100</v>
       </c>
       <c r="Z27">
-        <v>73.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -6381,10 +6447,10 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U28">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -6393,13 +6459,13 @@
         <v>93.8</v>
       </c>
       <c r="X28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y28">
         <v>100</v>
       </c>
       <c r="Z28">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="AA28">
         <v>100</v>
@@ -6467,31 +6533,31 @@
         <v>93.3</v>
       </c>
       <c r="T29">
-        <v>86.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U29">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="V29">
         <v>100</v>
       </c>
       <c r="W29">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X29">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="Y29">
         <v>100</v>
       </c>
       <c r="Z29">
-        <v>66.7</v>
+        <v>49.2</v>
       </c>
       <c r="AA29">
         <v>100</v>
       </c>
       <c r="AB29">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="30" spans="1:28">
@@ -6553,10 +6619,10 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U30">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6565,13 +6631,13 @@
         <v>93.8</v>
       </c>
       <c r="X30">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y30">
         <v>100</v>
       </c>
       <c r="Z30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="AA30">
         <v>100</v>
@@ -6639,7 +6705,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -6651,13 +6717,13 @@
         <v>93.8</v>
       </c>
       <c r="X31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Y31">
         <v>100</v>
       </c>
       <c r="Z31">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="AA31">
         <v>100</v>
@@ -6734,16 +6800,16 @@
         <v>100</v>
       </c>
       <c r="W32">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X32">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y32">
         <v>100</v>
       </c>
       <c r="Z32">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA32">
         <v>100</v>
@@ -6835,7 +6901,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -6844,19 +6910,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2">
-        <v>20.7</v>
+        <v>44.8</v>
       </c>
       <c r="G3" s="2">
-        <v>79.3</v>
+        <v>55.2</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6876,19 +6942,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>44.8</v>
+        <v>65.5</v>
       </c>
       <c r="G4" s="2">
-        <v>55.2</v>
+        <v>34.5</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6899,7 +6965,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -6908,19 +6974,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>48.3</v>
+        <v>86.2</v>
       </c>
       <c r="G5" s="2">
-        <v>51.7</v>
+        <v>13.8</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6940,19 +7006,19 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>62.1</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>37.9</v>
+        <v>6.9</v>
       </c>
       <c r="H6">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6963,7 +7029,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -6972,19 +7038,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>69</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>31</v>
+        <v>6.9</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6995,7 +7061,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
@@ -7004,19 +7070,19 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>79.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>20.7</v>
+        <v>3.4</v>
       </c>
       <c r="H8">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7027,7 +7093,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>63</v>
@@ -7036,19 +7102,19 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>82.8</v>
+        <v>100</v>
       </c>
       <c r="G9" s="2">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7059,7 +7125,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>64</v>
@@ -7068,19 +7134,19 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7130,7 +7196,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7162,22 +7228,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920218</v>
+        <v>23330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7185,16 +7251,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920218</v>
+        <v>23330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -7214,10 +7280,10 @@
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7237,10 +7303,10 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -7254,16 +7320,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920247</v>
+        <v>23330051920229</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7277,16 +7343,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920247</v>
+        <v>23330051920229</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -7300,19 +7366,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920258</v>
+        <v>23330051920241</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>57</v>
@@ -7323,16 +7389,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920258</v>
+        <v>23330051920241</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -7346,19 +7412,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920265</v>
+        <v>23330051920243</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>57</v>
@@ -7369,16 +7435,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920265</v>
+        <v>23330051920243</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -7392,39 +7458,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920221</v>
+        <v>23330051920335</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920223</v>
+        <v>23330051920335</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -7438,39 +7504,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920404</v>
+        <v>23330051920249</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920318</v>
+        <v>23330051920249</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -7479,6 +7545,328 @@
         <v>56</v>
       </c>
       <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920253</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920253</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920273</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920273</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920218</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920221</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920223</v>
+      </c>
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920404</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920228</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920245</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920247</v>
+      </c>
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920318</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920258</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920265</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20232.xlsx
+++ b/grupos/2ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -188,15 +188,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
@@ -227,6 +227,21 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>CUAPIO</t>
   </si>
   <si>
@@ -236,10 +251,7 @@
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>LUIS</t>
@@ -251,75 +263,60 @@
     <t>VEGA</t>
   </si>
   <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
     <t>MONDRAGON</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KARINA</t>
   </si>
   <si>
     <t>JESSICA</t>
   </si>
   <si>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
     <t>JAIRO</t>
   </si>
   <si>
@@ -329,46 +326,13 @@
     <t>MARYSOL</t>
   </si>
   <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
+    <t>RAYMUNDO</t>
   </si>
   <si>
     <t>ANGEL ADRIAN</t>
   </si>
   <si>
     <t>MIREILLE</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>FRANCISCO XAVIER</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="AJ4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK4">
         <v>8</v>
@@ -1121,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="AJ5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK5">
         <v>5</v>
@@ -1234,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="AJ6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK6">
         <v>6</v>
@@ -1347,7 +1311,7 @@
         <v>6</v>
       </c>
       <c r="AJ7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK7">
         <v>8</v>
@@ -1460,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="AJ8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK8">
         <v>7</v>
@@ -1573,7 +1537,7 @@
         <v>6</v>
       </c>
       <c r="AJ9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK9">
         <v>7</v>
@@ -1686,7 +1650,7 @@
         <v>7</v>
       </c>
       <c r="AJ10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK10">
         <v>7</v>
@@ -1799,7 +1763,7 @@
         <v>7</v>
       </c>
       <c r="AJ11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK11">
         <v>7</v>
@@ -1912,7 +1876,7 @@
         <v>6</v>
       </c>
       <c r="AJ12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK12">
         <v>8</v>
@@ -2025,7 +1989,7 @@
         <v>6</v>
       </c>
       <c r="AJ13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK13">
         <v>7</v>
@@ -2138,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="AJ14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK14">
         <v>5</v>
@@ -2251,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="AJ15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK15">
         <v>7</v>
@@ -2364,7 +2328,7 @@
         <v>5</v>
       </c>
       <c r="AJ16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK16">
         <v>6</v>
@@ -2477,7 +2441,7 @@
         <v>5</v>
       </c>
       <c r="AJ17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK17">
         <v>5</v>
@@ -2590,7 +2554,7 @@
         <v>5</v>
       </c>
       <c r="AJ18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK18">
         <v>6</v>
@@ -2703,7 +2667,7 @@
         <v>5</v>
       </c>
       <c r="AJ19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK19">
         <v>6</v>
@@ -2816,7 +2780,7 @@
         <v>5</v>
       </c>
       <c r="AJ20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK20">
         <v>7</v>
@@ -2929,7 +2893,7 @@
         <v>5</v>
       </c>
       <c r="AJ21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK21">
         <v>6</v>
@@ -3042,7 +3006,7 @@
         <v>6</v>
       </c>
       <c r="AJ22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK22">
         <v>7</v>
@@ -3155,7 +3119,7 @@
         <v>6</v>
       </c>
       <c r="AJ23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK23">
         <v>9</v>
@@ -3268,7 +3232,7 @@
         <v>5</v>
       </c>
       <c r="AJ24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK24">
         <v>7</v>
@@ -3381,7 +3345,7 @@
         <v>5</v>
       </c>
       <c r="AJ25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK25">
         <v>7</v>
@@ -3494,7 +3458,7 @@
         <v>6</v>
       </c>
       <c r="AJ26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK26">
         <v>9</v>
@@ -3607,7 +3571,7 @@
         <v>6</v>
       </c>
       <c r="AJ27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK27">
         <v>8</v>
@@ -3720,7 +3684,7 @@
         <v>5</v>
       </c>
       <c r="AJ28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK28">
         <v>6</v>
@@ -3833,7 +3797,7 @@
         <v>5</v>
       </c>
       <c r="AJ29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK29">
         <v>5</v>
@@ -3946,7 +3910,7 @@
         <v>6</v>
       </c>
       <c r="AJ30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK30">
         <v>7</v>
@@ -4059,7 +4023,7 @@
         <v>5</v>
       </c>
       <c r="AJ31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK31">
         <v>6</v>
@@ -4172,7 +4136,7 @@
         <v>5</v>
       </c>
       <c r="AJ32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK32">
         <v>9</v>
@@ -6872,7 +6836,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -6881,27 +6845,30 @@
         <v>29</v>
       </c>
       <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2">
+        <v>44.8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>55.2</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>29</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -6910,19 +6877,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>44.8</v>
+        <v>65.5</v>
       </c>
       <c r="G3" s="2">
-        <v>55.2</v>
+        <v>34.5</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6933,7 +6900,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -6942,19 +6909,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>65.5</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2">
-        <v>34.5</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7196,7 +7163,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7228,22 +7195,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920222</v>
+        <v>23330051920233</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7251,45 +7218,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920222</v>
+        <v>23330051920233</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>56</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920230</v>
+        <v>23330051920243</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7297,45 +7264,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920230</v>
+        <v>23330051920243</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920229</v>
+        <v>23330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7343,42 +7310,42 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920229</v>
+        <v>23330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920241</v>
+        <v>23330051920264</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>57</v>
@@ -7389,42 +7356,42 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920241</v>
+        <v>23330051920264</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920243</v>
+        <v>23330051920267</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>57</v>
@@ -7435,45 +7402,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920243</v>
+        <v>23330051920267</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>56</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920335</v>
+        <v>23330051920222</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7481,42 +7448,42 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920335</v>
+        <v>23330051920228</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920249</v>
+        <v>23330051920230</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>57</v>
@@ -7527,45 +7494,45 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920249</v>
+        <v>23330051920229</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920253</v>
+        <v>23330051920241</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7573,45 +7540,45 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920253</v>
+        <v>23330051920247</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920273</v>
+        <v>23330051920249</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7619,255 +7586,48 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920273</v>
+        <v>23330051920253</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
         <v>56</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920218</v>
+        <v>23330051920273</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>56</v>
       </c>
       <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920221</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920223</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920404</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920228</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920245</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920247</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920318</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920258</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920265</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ALCV - Estadisticos 20232.xlsx
+++ b/grupos/2ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="104">
   <si>
     <t>Materia</t>
   </si>
@@ -194,18 +194,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -227,33 +227,33 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GILES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>LAGUNA</t>
   </si>
   <si>
     <t>LOBATO</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
@@ -263,70 +263,67 @@
     <t>VEGA</t>
   </si>
   <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
     <t>TZITZIHUA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>NATH</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
     <t>MONDRAGON</t>
   </si>
   <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
     <t>MIRIAM</t>
   </si>
   <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
     <t>AARON ZACHARY</t>
   </si>
   <si>
     <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARYSOL</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
   </si>
   <si>
     <t>ANGEL ADRIAN</t>
@@ -939,13 +936,13 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>9</v>
@@ -1052,13 +1049,13 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -1079,7 +1076,7 @@
         <v>6</v>
       </c>
       <c r="AH5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI5">
         <v>5</v>
@@ -1165,13 +1162,13 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>6</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1192,13 +1189,13 @@
         <v>5</v>
       </c>
       <c r="AH6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI6">
         <v>5</v>
       </c>
       <c r="AJ6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK6">
         <v>6</v>
@@ -1278,13 +1275,13 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1391,13 +1388,13 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>9</v>
@@ -1504,13 +1501,13 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>6</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1531,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="AH9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI9">
         <v>6</v>
@@ -1617,13 +1614,13 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB10">
         <v>8</v>
@@ -1730,13 +1727,13 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1757,13 +1754,13 @@
         <v>8</v>
       </c>
       <c r="AH11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI11">
         <v>7</v>
       </c>
       <c r="AJ11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK11">
         <v>7</v>
@@ -1843,13 +1840,13 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1870,7 +1867,7 @@
         <v>6</v>
       </c>
       <c r="AH12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI12">
         <v>6</v>
@@ -1956,13 +1953,13 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>6</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -2069,13 +2066,13 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -2102,7 +2099,7 @@
         <v>5</v>
       </c>
       <c r="AJ14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK14">
         <v>5</v>
@@ -2182,13 +2179,13 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -2295,13 +2292,13 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2408,13 +2405,13 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2435,7 +2432,7 @@
         <v>6</v>
       </c>
       <c r="AH17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI17">
         <v>5</v>
@@ -2521,13 +2518,13 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>6</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB18">
         <v>8</v>
@@ -2548,13 +2545,13 @@
         <v>5</v>
       </c>
       <c r="AH18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI18">
         <v>5</v>
       </c>
       <c r="AJ18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK18">
         <v>6</v>
@@ -2634,13 +2631,13 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2747,13 +2744,13 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>6</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>8</v>
@@ -2780,7 +2777,7 @@
         <v>5</v>
       </c>
       <c r="AJ20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK20">
         <v>7</v>
@@ -2860,13 +2857,13 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2893,7 +2890,7 @@
         <v>5</v>
       </c>
       <c r="AJ21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK21">
         <v>6</v>
@@ -2973,13 +2970,13 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>6</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -3086,13 +3083,13 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>6</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -3119,7 +3116,7 @@
         <v>6</v>
       </c>
       <c r="AJ23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK23">
         <v>9</v>
@@ -3199,13 +3196,13 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB24">
         <v>8</v>
@@ -3312,13 +3309,13 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -3425,13 +3422,13 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>6</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB26">
         <v>9</v>
@@ -3538,13 +3535,13 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z27">
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>9</v>
@@ -3651,13 +3648,13 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z28">
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -3764,13 +3761,13 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z29">
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB29">
         <v>5</v>
@@ -3877,13 +3874,13 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>6</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -3990,13 +3987,13 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>6</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>7</v>
@@ -4103,13 +4100,13 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>6</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB32">
         <v>9</v>
@@ -4454,7 +4451,7 @@
         <v>78.7</v>
       </c>
       <c r="AA5">
-        <v>91.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AB5">
         <v>100</v>
@@ -4540,7 +4537,7 @@
         <v>78.7</v>
       </c>
       <c r="AA6">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AB6">
         <v>95.8</v>
@@ -5400,7 +5397,7 @@
         <v>78.7</v>
       </c>
       <c r="AA16">
-        <v>61.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AB16">
         <v>100</v>
@@ -5572,7 +5569,7 @@
         <v>91.8</v>
       </c>
       <c r="AA18">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AB18">
         <v>95.8</v>
@@ -5744,7 +5741,7 @@
         <v>85.2</v>
       </c>
       <c r="AA20">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AB20">
         <v>100</v>
@@ -6002,7 +5999,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="AA23">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AB23">
         <v>100</v>
@@ -6088,7 +6085,7 @@
         <v>95.09999999999999</v>
       </c>
       <c r="AA24">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AB24">
         <v>100</v>
@@ -6518,7 +6515,7 @@
         <v>49.2</v>
       </c>
       <c r="AA29">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="AB29">
         <v>95.8</v>
@@ -6900,7 +6897,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -6909,19 +6906,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>69</v>
+        <v>86.2</v>
       </c>
       <c r="G4" s="2">
-        <v>31</v>
+        <v>13.8</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6932,7 +6929,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -6941,16 +6938,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="G5" s="2">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="H5">
         <v>6.8</v>
@@ -6996,7 +6993,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -7017,7 +7014,7 @@
         <v>6.9</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7163,7 +7160,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7195,7 +7192,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920233</v>
+        <v>23330051920231</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
@@ -7207,10 +7204,10 @@
         <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7218,7 +7215,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920233</v>
+        <v>23330051920231</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
@@ -7230,10 +7227,10 @@
         <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7241,7 +7238,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920243</v>
+        <v>23330051920233</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
@@ -7253,10 +7250,10 @@
         <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7264,7 +7261,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920243</v>
+        <v>23330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -7276,10 +7273,10 @@
         <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7287,7 +7284,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920335</v>
+        <v>23330051920271</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -7299,10 +7296,10 @@
         <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7310,7 +7307,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920335</v>
+        <v>23330051920271</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -7322,10 +7319,10 @@
         <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7425,7 +7422,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920222</v>
+        <v>23330051920230</v>
       </c>
       <c r="B12" t="s">
         <v>74</v>
@@ -7437,10 +7434,10 @@
         <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7448,10 +7445,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920228</v>
+        <v>23330051920229</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>87</v>
@@ -7460,10 +7457,10 @@
         <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7471,22 +7468,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920230</v>
+        <v>23330051920241</v>
       </c>
       <c r="B14" t="s">
         <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7494,22 +7491,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920229</v>
+        <v>23330051920243</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7517,13 +7514,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920241</v>
+        <v>23330051920335</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>101</v>
@@ -7540,22 +7537,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920247</v>
+        <v>23330051920249</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7563,16 +7560,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920249</v>
+        <v>23330051920253</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
@@ -7586,13 +7583,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920253</v>
+        <v>23330051920273</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -7604,29 +7601,6 @@
         <v>56</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920273</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>
